--- a/output/fatores_condicionantes_base_monetaria_anual.xlsx
+++ b/output/fatores_condicionantes_base_monetaria_anual.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Variacao_no_ano" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Valor_dezembro_SGS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Saldo_ultimo_dia_ano" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Variacao_no_ano" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Agregado_anual_longo" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Codigos_SGS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,26 +490,6 @@
           <t>base_monetaria_restrita</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>soma_fatores</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>saldo_base</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>variacao_base</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>discrepancia</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -517,43 +497,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1995-12-01</t>
+          <t>1995-12-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-3979.704</v>
+        <v>913.253</v>
       </c>
       <c r="E2" t="n">
-        <v>-14604.987</v>
+        <v>2456.133</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>14900.094</v>
+        <v>268.337</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>4075.931</v>
+        <v>941.3390000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>2977.769</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>3369.103</v>
-      </c>
-      <c r="P2" t="n">
+        <v>385.638</v>
+      </c>
+      <c r="N2" t="n">
         <v>21681.591</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -561,48 +535,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1996-12-01</t>
+          <t>1996-12-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5513.388</v>
+        <v>443.623</v>
       </c>
       <c r="E3" t="n">
-        <v>-29670.499</v>
+        <v>2309.305</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>9988.201999999999</v>
+        <v>234.088</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-2146.231</v>
+        <v>-1399.092</v>
       </c>
       <c r="M3" t="n">
-        <v>10027.648</v>
+        <v>3491.052</v>
       </c>
       <c r="N3" t="n">
-        <v>-1885.894</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-6287.492000000002</v>
-      </c>
-      <c r="P3" t="n">
         <v>19795.697</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-1885.894</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-4401.598000000002</v>
       </c>
     </row>
     <row r="4">
@@ -611,48 +573,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-12-31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-5074.927</v>
+        <v>-1614.296</v>
       </c>
       <c r="E4" t="n">
-        <v>22158.7</v>
+        <v>9731.575999999999</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-9049.683000000001</v>
+        <v>-653.4160000000001</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-8790.445</v>
+        <v>-572.405</v>
       </c>
       <c r="M4" t="n">
-        <v>1698.923</v>
+        <v>-392.392</v>
       </c>
       <c r="N4" t="n">
-        <v>12032.635</v>
-      </c>
-      <c r="O4" t="n">
-        <v>942.5680000000004</v>
-      </c>
-      <c r="P4" t="n">
         <v>31828.332</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>12032.635</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-11090.067</v>
       </c>
     </row>
     <row r="5">
@@ -661,48 +611,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-12-31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-15106.533</v>
+        <v>-691.282</v>
       </c>
       <c r="E5" t="n">
-        <v>27854.801</v>
+        <v>7008.447</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-21429.065</v>
+        <v>-6553.666</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>20282.878</v>
+        <v>8.602</v>
       </c>
       <c r="M5" t="n">
-        <v>179.863</v>
+        <v>-17.107</v>
       </c>
       <c r="N5" t="n">
-        <v>7356.046</v>
-      </c>
-      <c r="O5" t="n">
-        <v>11781.944</v>
-      </c>
-      <c r="P5" t="n">
         <v>39184.378</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7356.045999999998</v>
-      </c>
-      <c r="R5" t="n">
-        <v>4425.898000000003</v>
       </c>
     </row>
     <row r="6">
@@ -711,48 +649,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-12-31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-15563.288</v>
+        <v>221.121</v>
       </c>
       <c r="E6" t="n">
-        <v>34925.161</v>
+        <v>13671.946</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-14877.571</v>
+        <v>-2758.67</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>2114.291</v>
+        <v>8.346</v>
       </c>
       <c r="M6" t="n">
-        <v>32.201</v>
+        <v>-34.728</v>
       </c>
       <c r="N6" t="n">
-        <v>9245.779</v>
-      </c>
-      <c r="O6" t="n">
-        <v>6630.794</v>
-      </c>
-      <c r="P6" t="n">
         <v>48430.157</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>9245.779000000002</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-2614.985000000002</v>
       </c>
     </row>
     <row r="7">
@@ -761,50 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2000-12-01</t>
+          <t>2000-12-31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-26539.148</v>
+        <v>-90.184</v>
       </c>
       <c r="E7" t="n">
-        <v>21398.839</v>
+        <v>9094.619000000001</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>4402.641</v>
+        <v>-1941.905</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>-614.971</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>1478.559</v>
+        <v>-127.452</v>
       </c>
       <c r="M7" t="n">
-        <v>-839.2619999999999</v>
+        <v>20.253</v>
       </c>
       <c r="N7" t="n">
-        <v>-743.944</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-713.3420000000015</v>
-      </c>
-      <c r="P7" t="n">
         <v>47686.213</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-743.9439999999959</v>
-      </c>
-      <c r="R7" t="n">
-        <v>30.6019999999944</v>
       </c>
     </row>
     <row r="8">
@@ -813,24 +727,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-11944.926</v>
+        <v>8397.878000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>41318.272</v>
+        <v>1536.537</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>-18572.367</v>
+        <v>-2232.312</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
@@ -838,25 +752,13 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>-1806.911</v>
+        <v>-614.102</v>
       </c>
       <c r="M8" t="n">
-        <v>-3424.281</v>
+        <v>-66.297</v>
       </c>
       <c r="N8" t="n">
-        <v>5569.758</v>
-      </c>
-      <c r="O8" t="n">
-        <v>5569.786999999999</v>
-      </c>
-      <c r="P8" t="n">
         <v>53255.971</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5569.757999999994</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.02900000000499858</v>
       </c>
     </row>
     <row r="9">
@@ -865,52 +767,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-12-31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-20483.697</v>
+        <v>196.734</v>
       </c>
       <c r="E9" t="n">
-        <v>90722.091</v>
+        <v>15954.153</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-26426.605</v>
+        <v>-4981.6</v>
       </c>
       <c r="I9" t="n">
-        <v>10564.64</v>
+        <v>1707.304</v>
       </c>
       <c r="J9" t="n">
-        <v>400.375</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>-33769.655</v>
+        <v>-276.31</v>
       </c>
       <c r="M9" t="n">
-        <v>-1338.211</v>
+        <v>143.984</v>
       </c>
       <c r="N9" t="n">
-        <v>20046.301</v>
-      </c>
-      <c r="O9" t="n">
-        <v>19668.93800000001</v>
-      </c>
-      <c r="P9" t="n">
         <v>73302.272</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>20046.301</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-377.3629999999939</v>
       </c>
     </row>
     <row r="10">
@@ -919,52 +809,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-12-31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1064.493</v>
+        <v>11711.648</v>
       </c>
       <c r="E10" t="n">
-        <v>11180.802</v>
+        <v>3231.403</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>643.224</v>
+        <v>13.499</v>
       </c>
       <c r="I10" t="n">
-        <v>-15632.065</v>
+        <v>-2507.953</v>
       </c>
       <c r="J10" t="n">
-        <v>2.247</v>
+        <v>-3.965</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>6729.147</v>
+        <v>-1665.84</v>
       </c>
       <c r="M10" t="n">
-        <v>-1941.998</v>
+        <v>22.977</v>
       </c>
       <c r="N10" t="n">
-        <v>-83.136</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-83.13600000000088</v>
-      </c>
-      <c r="P10" t="n">
         <v>73219.136</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-83.1359999999986</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-2.273736754432321e-12</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +851,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-48292.47</v>
+        <v>-2788.872</v>
       </c>
       <c r="E11" t="n">
-        <v>57838.483</v>
+        <v>12183.568</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>14556.008</v>
+        <v>7186.047</v>
       </c>
       <c r="I11" t="n">
-        <v>-6032.014</v>
+        <v>-1581.56</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.14</v>
+        <v>-1.331</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>-2400.391</v>
+        <v>-1577.674</v>
       </c>
       <c r="M11" t="n">
-        <v>-148.935</v>
+        <v>214.898</v>
       </c>
       <c r="N11" t="n">
-        <v>15513.541</v>
-      </c>
-      <c r="O11" t="n">
-        <v>15513.541</v>
-      </c>
-      <c r="P11" t="n">
         <v>88732.677</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>15513.541</v>
-      </c>
-      <c r="R11" t="n">
-        <v>5.456968210637569e-12</v>
       </c>
     </row>
     <row r="12">
@@ -1027,52 +893,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-43007.731</v>
+        <v>-1519.602</v>
       </c>
       <c r="E12" t="n">
-        <v>2808.482</v>
+        <v>9945.445</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>52394.883</v>
+        <v>9261.061</v>
       </c>
       <c r="I12" t="n">
-        <v>-2684.423</v>
+        <v>-172.064</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.343</v>
+        <v>-0.102</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>2373.784</v>
+        <v>-1927.55</v>
       </c>
       <c r="M12" t="n">
-        <v>632.9059999999999</v>
+        <v>144.777</v>
       </c>
       <c r="N12" t="n">
-        <v>12514.558</v>
-      </c>
-      <c r="O12" t="n">
-        <v>12514.558</v>
-      </c>
-      <c r="P12" t="n">
         <v>101247.235</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>12514.558</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1081,52 +935,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-59510.709</v>
+        <v>-2159.061</v>
       </c>
       <c r="E13" t="n">
-        <v>-686.574</v>
+        <v>13309.467</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>74368.942</v>
+        <v>5568.509</v>
       </c>
       <c r="I13" t="n">
-        <v>5436.454</v>
+        <v>498.916</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.476</v>
+        <v>-0.039</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-764.37</v>
+        <v>-1645.963</v>
       </c>
       <c r="M13" t="n">
-        <v>1012.499</v>
+        <v>195.164</v>
       </c>
       <c r="N13" t="n">
-        <v>19854.766</v>
-      </c>
-      <c r="O13" t="n">
-        <v>19854.76599999999</v>
-      </c>
-      <c r="P13" t="n">
         <v>121102.001</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>19854.766</v>
-      </c>
-      <c r="R13" t="n">
-        <v>-1.091393642127514e-11</v>
       </c>
     </row>
     <row r="14">
@@ -1135,52 +977,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-12-31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-55600.882</v>
+        <v>-4826.282</v>
       </c>
       <c r="E14" t="n">
-        <v>-73974.527</v>
+        <v>19229.181</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>155390.627</v>
+        <v>4210.354</v>
       </c>
       <c r="I14" t="n">
-        <v>8812.156000000001</v>
+        <v>484.911</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.017</v>
+        <v>-0.05</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>-10600.939</v>
+        <v>-3466.24</v>
       </c>
       <c r="M14" t="n">
-        <v>1491.448</v>
+        <v>137.516</v>
       </c>
       <c r="N14" t="n">
-        <v>25514.866</v>
-      </c>
-      <c r="O14" t="n">
-        <v>25514.86600000001</v>
-      </c>
-      <c r="P14" t="n">
         <v>146616.867</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>25514.86599999999</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.818989403545856e-11</v>
       </c>
     </row>
     <row r="15">
@@ -1189,52 +1019,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-12-31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-74312.39599999999</v>
+        <v>-3477.074</v>
       </c>
       <c r="E15" t="n">
-        <v>34058.554</v>
+        <v>-18947.937</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-12124.211</v>
+        <v>-7846.766</v>
       </c>
       <c r="I15" t="n">
-        <v>-4801.25</v>
+        <v>983.582</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.073</v>
+        <v>-0.007</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>57041.22</v>
+        <v>44336.711</v>
       </c>
       <c r="M15" t="n">
-        <v>1071.994</v>
+        <v>182.436</v>
       </c>
       <c r="N15" t="n">
-        <v>932.838</v>
-      </c>
-      <c r="O15" t="n">
-        <v>932.8380000000045</v>
-      </c>
-      <c r="P15" t="n">
         <v>147549.705</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>932.8379999999888</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.568878360558301e-11</v>
       </c>
     </row>
     <row r="16">
@@ -1243,52 +1061,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-12-31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-52311.507</v>
+        <v>-15185.319</v>
       </c>
       <c r="E16" t="n">
-        <v>11280.602</v>
+        <v>19521.306</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>62936.723</v>
+        <v>6337.003</v>
       </c>
       <c r="I16" t="n">
-        <v>-3198.916</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.181</v>
+        <v>-0.031</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>-3425.469</v>
+        <v>-2009.398</v>
       </c>
       <c r="M16" t="n">
-        <v>3242.878</v>
+        <v>541.211</v>
       </c>
       <c r="N16" t="n">
-        <v>18523.13</v>
-      </c>
-      <c r="O16" t="n">
-        <v>18523.13</v>
-      </c>
-      <c r="P16" t="n">
         <v>166072.835</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>18523.13</v>
-      </c>
-      <c r="R16" t="n">
-        <v>-7.275957614183426e-12</v>
       </c>
     </row>
     <row r="17">
@@ -1297,52 +1103,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2010-12-01</t>
+          <t>2010-12-31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-51203.673</v>
+        <v>-22880.052</v>
       </c>
       <c r="E17" t="n">
-        <v>249513.458</v>
+        <v>111543.835</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>75552.632</v>
+        <v>4276.126</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.539</v>
+        <v>-134.314</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>-236911.071</v>
+        <v>-65142.76</v>
       </c>
       <c r="M17" t="n">
-        <v>3829.68</v>
+        <v>704.9690000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>40780.487</v>
-      </c>
-      <c r="O17" t="n">
-        <v>40780.48700000003</v>
-      </c>
-      <c r="P17" t="n">
         <v>206853.322</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>40780.48699999999</v>
-      </c>
-      <c r="R17" t="n">
-        <v>3.637978807091713e-11</v>
       </c>
     </row>
     <row r="18">
@@ -1351,52 +1145,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2011-12-01</t>
+          <t>2011-12-31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-125632.863</v>
+        <v>-17945.76</v>
       </c>
       <c r="E18" t="n">
-        <v>70196.20299999999</v>
+        <v>44910.037</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>85156.228</v>
+        <v>303.625</v>
       </c>
       <c r="I18" t="n">
-        <v>-705.683</v>
+        <v>-31.85</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.001</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>-24388.014</v>
+        <v>4361.607</v>
       </c>
       <c r="M18" t="n">
-        <v>2756.678</v>
+        <v>-33.262</v>
       </c>
       <c r="N18" t="n">
-        <v>7381.989</v>
-      </c>
-      <c r="O18" t="n">
-        <v>7381.988999999998</v>
-      </c>
-      <c r="P18" t="n">
         <v>214235.311</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>7381.989000000001</v>
-      </c>
-      <c r="R18" t="n">
-        <v>-3.637978807091713e-12</v>
       </c>
     </row>
     <row r="19">
@@ -1405,52 +1187,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2012-12-01</t>
+          <t>2012-12-31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-121648.972</v>
+        <v>-39380.522</v>
       </c>
       <c r="E19" t="n">
-        <v>5653.172</v>
+        <v>64648.943</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>25896.973</v>
+        <v>-10975.444</v>
       </c>
       <c r="I19" t="n">
-        <v>-1100.801</v>
+        <v>-59.77</v>
       </c>
       <c r="J19" t="n">
-        <v>45.943</v>
+        <v>-5.424</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>118682.701</v>
+        <v>3161.327</v>
       </c>
       <c r="M19" t="n">
-        <v>-8392.875</v>
+        <v>6957.731</v>
       </c>
       <c r="N19" t="n">
-        <v>19136.141</v>
-      </c>
-      <c r="O19" t="n">
-        <v>19136.141</v>
-      </c>
-      <c r="P19" t="n">
         <v>233371.452</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>19136.141</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1459,52 +1229,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2013-12-01</t>
+          <t>2013-12-31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-127554.789</v>
+        <v>-43098.963</v>
       </c>
       <c r="E20" t="n">
-        <v>197242.065</v>
+        <v>88570.25199999999</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-22428.624</v>
+        <v>-6973.532</v>
       </c>
       <c r="I20" t="n">
-        <v>1314.564</v>
+        <v>48.593</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.675</v>
+        <v>-0.002</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>-19903.346</v>
+        <v>-7111.959</v>
       </c>
       <c r="M20" t="n">
-        <v>-12532.941</v>
+        <v>2528.586</v>
       </c>
       <c r="N20" t="n">
-        <v>16138.326</v>
-      </c>
-      <c r="O20" t="n">
-        <v>16135.254</v>
-      </c>
-      <c r="P20" t="n">
         <v>249509.778</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>16138.326</v>
-      </c>
-      <c r="R20" t="n">
-        <v>-3.072000000005573</v>
       </c>
     </row>
     <row r="21">
@@ -1513,52 +1271,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2014-12-31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-668.486</v>
+        <v>-17938.494</v>
       </c>
       <c r="E21" t="n">
-        <v>-76307.204</v>
+        <v>43320.612</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>16274.839</v>
+        <v>-27192.559</v>
       </c>
       <c r="I21" t="n">
-        <v>17329.053</v>
+        <v>17044.874</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.045</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>56163.369</v>
+        <v>6483.102</v>
       </c>
       <c r="M21" t="n">
-        <v>1227.406</v>
+        <v>185.497</v>
       </c>
       <c r="N21" t="n">
-        <v>14018.739</v>
-      </c>
-      <c r="O21" t="n">
-        <v>14018.932</v>
-      </c>
-      <c r="P21" t="n">
         <v>263528.517</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>14018.739</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.1929999999956635</v>
       </c>
     </row>
     <row r="22">
@@ -1567,56 +1313,44 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-12-31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>59665.808</v>
+        <v>31966.901</v>
       </c>
       <c r="E22" t="n">
-        <v>-124016.063</v>
+        <v>-18963.647</v>
       </c>
       <c r="F22" t="n">
-        <v>-123479.463</v>
+        <v>-41100.11</v>
       </c>
       <c r="G22" t="n">
-        <v>-536.6</v>
+        <v>22136.463</v>
       </c>
       <c r="H22" t="n">
-        <v>-15037.71</v>
+        <v>-1077.38</v>
       </c>
       <c r="I22" t="n">
-        <v>89657.15300000001</v>
+        <v>7794.459</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.593</v>
+        <v>-1.959</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>-24740.332</v>
+        <v>-7713.625</v>
       </c>
       <c r="M22" t="n">
-        <v>6233.098</v>
+        <v>437.373</v>
       </c>
       <c r="N22" t="n">
-        <v>-8239.594999999999</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-8238.63899999999</v>
-      </c>
-      <c r="P22" t="n">
         <v>255288.922</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-8239.595000000001</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.9560000000110449</v>
       </c>
     </row>
     <row r="23">
@@ -1625,56 +1359,44 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-12-31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12284.191</v>
+        <v>-52397.634</v>
       </c>
       <c r="E23" t="n">
-        <v>32267.88</v>
+        <v>79414.034</v>
       </c>
       <c r="F23" t="n">
-        <v>31896.944</v>
+        <v>7559.278</v>
       </c>
       <c r="G23" t="n">
-        <v>370.936</v>
+        <v>71854.75599999999</v>
       </c>
       <c r="H23" t="n">
-        <v>32532.733</v>
+        <v>352.478</v>
       </c>
       <c r="I23" t="n">
-        <v>-75562.37300000001</v>
+        <v>-3858.12</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.179</v>
+        <v>-0.027</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>6054.528</v>
+        <v>1612.164</v>
       </c>
       <c r="M23" t="n">
-        <v>7424.617</v>
+        <v>244.327</v>
       </c>
       <c r="N23" t="n">
-        <v>14998.224</v>
-      </c>
-      <c r="O23" t="n">
-        <v>14998.397</v>
-      </c>
-      <c r="P23" t="n">
         <v>270287.146</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>14998.22400000002</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.1729999999806751</v>
       </c>
     </row>
     <row r="24">
@@ -1683,56 +1405,44 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>52132.877</v>
+        <v>7163.59</v>
       </c>
       <c r="E24" t="n">
-        <v>-26792.966</v>
+        <v>45249.193</v>
       </c>
       <c r="F24" t="n">
-        <v>-111168.532</v>
+        <v>-30684.804</v>
       </c>
       <c r="G24" t="n">
-        <v>84375.56600000001</v>
+        <v>75933.997</v>
       </c>
       <c r="H24" t="n">
-        <v>1396.743</v>
+        <v>-26027.013</v>
       </c>
       <c r="I24" t="n">
-        <v>-7032.535</v>
+        <v>1443.181</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.181</v>
+        <v>-8.92</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>867.627</v>
+        <v>4770.938</v>
       </c>
       <c r="M24" t="n">
-        <v>5896.818</v>
+        <v>-55.314</v>
       </c>
       <c r="N24" t="n">
-        <v>26468.31</v>
-      </c>
-      <c r="O24" t="n">
-        <v>26468.383</v>
-      </c>
-      <c r="P24" t="n">
         <v>296755.456</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>26468.31</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.07300000000032014</v>
       </c>
     </row>
     <row r="25">
@@ -1741,56 +1451,44 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-12-31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-44486.13</v>
+        <v>20453.395</v>
       </c>
       <c r="E25" t="n">
-        <v>35093.592</v>
+        <v>36530.769</v>
       </c>
       <c r="F25" t="n">
-        <v>32704.358</v>
+        <v>-29615.079</v>
       </c>
       <c r="G25" t="n">
-        <v>2389.234</v>
+        <v>66145.848</v>
       </c>
       <c r="H25" t="n">
-        <v>-17348.77</v>
+        <v>-30488.34</v>
       </c>
       <c r="I25" t="n">
-        <v>15125.016</v>
+        <v>1519.905</v>
       </c>
       <c r="J25" t="n">
-        <v>13.2</v>
+        <v>13.279</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>13987.567</v>
+        <v>-6759.022</v>
       </c>
       <c r="M25" t="n">
-        <v>2909.758</v>
+        <v>1520.697</v>
       </c>
       <c r="N25" t="n">
-        <v>5294.005</v>
-      </c>
-      <c r="O25" t="n">
-        <v>5294.232999999998</v>
-      </c>
-      <c r="P25" t="n">
         <v>302049.461</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5294.005000000005</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.227999999993699</v>
       </c>
     </row>
     <row r="26">
@@ -1799,56 +1497,44 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-12-31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-89301.052</v>
+        <v>-43975.649</v>
       </c>
       <c r="E26" t="n">
-        <v>227324.959</v>
+        <v>127568.06</v>
       </c>
       <c r="F26" t="n">
-        <v>-15720.656</v>
+        <v>-15623.582</v>
       </c>
       <c r="G26" t="n">
-        <v>243045.615</v>
+        <v>143191.642</v>
       </c>
       <c r="H26" t="n">
-        <v>-141168.328</v>
+        <v>-46838.632</v>
       </c>
       <c r="I26" t="n">
-        <v>7639.551</v>
+        <v>-6928.091</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.549</v>
+        <v>-0.06</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>16690.766</v>
+        <v>-6659.602</v>
       </c>
       <c r="M26" t="n">
-        <v>-6634.019</v>
+        <v>-3362.213</v>
       </c>
       <c r="N26" t="n">
-        <v>14537.246</v>
-      </c>
-      <c r="O26" t="n">
-        <v>14537.328</v>
-      </c>
-      <c r="P26" t="n">
         <v>316586.707</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>14537.24599999998</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.08200000001306762</v>
       </c>
     </row>
     <row r="27">
@@ -1857,58 +1543,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>704194.5379999999</v>
+        <v>25213.146</v>
       </c>
       <c r="E27" t="n">
-        <v>-630037.433</v>
+        <v>-19509.913</v>
       </c>
       <c r="F27" t="n">
-        <v>-365463.108</v>
+        <v>-179441.373</v>
       </c>
       <c r="G27" t="n">
-        <v>-264574.325</v>
+        <v>159931.46</v>
       </c>
       <c r="H27" t="n">
-        <v>-117733.553</v>
+        <v>-12809.786</v>
       </c>
       <c r="I27" t="n">
-        <v>40800.821</v>
+        <v>-8028.787</v>
       </c>
       <c r="J27" t="n">
-        <v>3.485</v>
+        <v>2.383</v>
       </c>
       <c r="K27" t="n">
-        <v>65828.662</v>
+        <v>27816.1</v>
       </c>
       <c r="L27" t="n">
-        <v>69829.095</v>
+        <v>3009.625</v>
       </c>
       <c r="M27" t="n">
-        <v>-19343.055</v>
+        <v>-1835.66</v>
       </c>
       <c r="N27" t="n">
-        <v>114949.946</v>
-      </c>
-      <c r="O27" t="n">
-        <v>113542.56</v>
-      </c>
-      <c r="P27" t="n">
         <v>431536.653</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>114949.946</v>
-      </c>
-      <c r="R27" t="n">
-        <v>-1407.385999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1917,58 +1591,46 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-81290.481</v>
+        <v>-42883.828</v>
       </c>
       <c r="E28" t="n">
-        <v>182431.271</v>
+        <v>76002.281</v>
       </c>
       <c r="F28" t="n">
-        <v>-121550.764</v>
+        <v>-61753.191</v>
       </c>
       <c r="G28" t="n">
-        <v>303982.035</v>
+        <v>137755.472</v>
       </c>
       <c r="H28" t="n">
-        <v>-36630.77</v>
+        <v>-35033.5</v>
       </c>
       <c r="I28" t="n">
-        <v>22323.949</v>
+        <v>3983.847</v>
       </c>
       <c r="J28" t="n">
-        <v>44.99</v>
+        <v>50.194</v>
       </c>
       <c r="K28" t="n">
-        <v>-52769.578</v>
+        <v>4765.473</v>
       </c>
       <c r="L28" t="n">
-        <v>-26059.891</v>
+        <v>246.624</v>
       </c>
       <c r="M28" t="n">
-        <v>-30402.627</v>
+        <v>-11219.235</v>
       </c>
       <c r="N28" t="n">
-        <v>-22353.134</v>
-      </c>
-      <c r="O28" t="n">
-        <v>-22353.13699999998</v>
-      </c>
-      <c r="P28" t="n">
         <v>409183.519</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-22353.13400000002</v>
-      </c>
-      <c r="R28" t="n">
-        <v>-0.002999999964231392</v>
       </c>
     </row>
     <row r="29">
@@ -1977,58 +1639,46 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-152518.591</v>
+        <v>-35780.006</v>
       </c>
       <c r="E29" t="n">
-        <v>437174.227</v>
+        <v>139533.68</v>
       </c>
       <c r="F29" t="n">
-        <v>251182.278</v>
+        <v>-22231.419</v>
       </c>
       <c r="G29" t="n">
-        <v>185991.949</v>
+        <v>161765.099</v>
       </c>
       <c r="H29" t="n">
-        <v>-56620.783</v>
+        <v>-46541.023</v>
       </c>
       <c r="I29" t="n">
-        <v>-92265.39999999999</v>
+        <v>-5739.568</v>
       </c>
       <c r="J29" t="n">
-        <v>-27.398</v>
+        <v>26.424</v>
       </c>
       <c r="K29" t="n">
-        <v>9097.299000000001</v>
+        <v>-17642.115</v>
       </c>
       <c r="L29" t="n">
-        <v>-54168.5</v>
+        <v>13351.98</v>
       </c>
       <c r="M29" t="n">
-        <v>-80194.454</v>
+        <v>-19082.092</v>
       </c>
       <c r="N29" t="n">
-        <v>10476.399</v>
-      </c>
-      <c r="O29" t="n">
-        <v>10476.40000000008</v>
-      </c>
-      <c r="P29" t="n">
         <v>419659.918</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>10476.39900000003</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.001000000047497451</v>
       </c>
     </row>
     <row r="30">
@@ -2037,58 +1687,46 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>206854.972</v>
+        <v>80331.787</v>
       </c>
       <c r="E30" t="n">
-        <v>-56588.088</v>
+        <v>-18023.368</v>
       </c>
       <c r="F30" t="n">
-        <v>73732.46000000001</v>
+        <v>-127402.891</v>
       </c>
       <c r="G30" t="n">
-        <v>-130320.548</v>
+        <v>109379.523</v>
       </c>
       <c r="H30" t="n">
-        <v>78236.91</v>
+        <v>233.715</v>
       </c>
       <c r="I30" t="n">
-        <v>-70871.662</v>
+        <v>-6628.462</v>
       </c>
       <c r="J30" t="n">
-        <v>-29.715</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>-33737.198</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>-45370.899</v>
+        <v>-16363.195</v>
       </c>
       <c r="M30" t="n">
-        <v>-75435.61500000001</v>
+        <v>-22381.99</v>
       </c>
       <c r="N30" t="n">
-        <v>3058.71</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3058.705000000031</v>
-      </c>
-      <c r="P30" t="n">
         <v>422718.628</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3058.710000000021</v>
-      </c>
-      <c r="R30" t="n">
-        <v>-0.004999999990104698</v>
       </c>
     </row>
     <row r="31">
@@ -2097,58 +1735,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>parcial</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>65831.935</v>
+        <v>-55712.578</v>
       </c>
       <c r="E31" t="n">
-        <v>158704.826</v>
+        <v>211370.114</v>
       </c>
       <c r="F31" t="n">
-        <v>65135.039</v>
+        <v>-30736.668</v>
       </c>
       <c r="G31" t="n">
-        <v>93569.787</v>
+        <v>242106.782</v>
       </c>
       <c r="H31" t="n">
-        <v>-212477.334</v>
+        <v>-186347.058</v>
       </c>
       <c r="I31" t="n">
-        <v>115930.245</v>
+        <v>19928.148</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.788</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.021</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>-706.95</v>
+        <v>35522.321</v>
       </c>
       <c r="M31" t="n">
-        <v>-98786.795</v>
+        <v>-10450.304</v>
       </c>
       <c r="N31" t="n">
-        <v>28494.96</v>
-      </c>
-      <c r="O31" t="n">
-        <v>28495.118</v>
-      </c>
-      <c r="P31" t="n">
         <v>451213.588</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>28494.95999999996</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.1580000000394648</v>
       </c>
     </row>
     <row r="32">
@@ -2157,56 +1783,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>94770.505</v>
+        <v>-35402.732</v>
       </c>
       <c r="E32" t="n">
-        <v>54036.513</v>
+        <v>73663.50999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>-376560.608</v>
+        <v>-77293.57799999999</v>
       </c>
       <c r="G32" t="n">
-        <v>430597.121</v>
+        <v>150957.088</v>
       </c>
       <c r="H32" t="n">
-        <v>8357.906000000001</v>
+        <v>-22296.357</v>
       </c>
       <c r="I32" t="n">
-        <v>-105895.906</v>
+        <v>18302.009</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
-        <v>-0.024</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>45376.981</v>
+        <v>-20160.853</v>
       </c>
       <c r="M32" t="n">
-        <v>-100762.164</v>
+        <v>2448.268</v>
       </c>
       <c r="N32" t="n">
-        <v>-4116.934</v>
-      </c>
-      <c r="O32" t="n">
-        <v>-4116.188999999998</v>
-      </c>
-      <c r="P32" t="n">
         <v>447096.654</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>-4116.934000000008</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.7450000000098953</v>
       </c>
     </row>
     <row r="33">
@@ -2215,7 +1829,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2224,47 +1838,35 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>131825.207</v>
+        <v>60858.785</v>
       </c>
       <c r="E33" t="n">
-        <v>-72034.109</v>
+        <v>-55189.171</v>
       </c>
       <c r="F33" t="n">
-        <v>20176.538</v>
+        <v>-125795.713</v>
       </c>
       <c r="G33" t="n">
-        <v>-92210.64599999999</v>
+        <v>70606.542</v>
       </c>
       <c r="H33" t="n">
-        <v>52583.317</v>
+        <v>2919.547</v>
       </c>
       <c r="I33" t="n">
-        <v>-62162.632</v>
+        <v>9276.611000000001</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
         <v>800</v>
       </c>
       <c r="L33" t="n">
-        <v>14472.391</v>
+        <v>3858.149</v>
       </c>
       <c r="M33" t="n">
-        <v>-81478.091</v>
+        <v>-19230.225</v>
       </c>
       <c r="N33" t="n">
-        <v>-15995.656</v>
-      </c>
-      <c r="O33" t="n">
-        <v>-15993.91699999999</v>
-      </c>
-      <c r="P33" t="n">
         <v>431100.998</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>-15995.65599999996</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.738999999972293</v>
       </c>
     </row>
   </sheetData>
@@ -2278,7 +1880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2352,6 +1954,26 @@
           <t>base_monetaria_restrita</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>soma_fatores</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>saldo_base</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>variacao_base</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>discrepancia</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2359,37 +1981,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1995-12-01</t>
+          <t>1995-12-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>913.253</v>
+        <v>-3979.704</v>
       </c>
       <c r="E2" t="n">
-        <v>2456.133</v>
+        <v>-14604.987</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>268.337</v>
+        <v>14900.094</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>941.3390000000001</v>
+        <v>4075.931</v>
       </c>
       <c r="M2" t="n">
-        <v>385.638</v>
-      </c>
-      <c r="N2" t="n">
+        <v>2977.769</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>3369.103</v>
+      </c>
+      <c r="P2" t="n">
         <v>21681.591</v>
       </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2397,36 +2025,48 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1996-12-01</t>
+          <t>1996-12-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>443.623</v>
+        <v>5513.388</v>
       </c>
       <c r="E3" t="n">
-        <v>2309.305</v>
+        <v>-29670.499</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>234.088</v>
+        <v>9988.201999999999</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-1399.092</v>
+        <v>-2146.231</v>
       </c>
       <c r="M3" t="n">
-        <v>3491.052</v>
+        <v>10027.648</v>
       </c>
       <c r="N3" t="n">
+        <v>-1885.894</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-6287.492000000002</v>
+      </c>
+      <c r="P3" t="n">
         <v>19795.697</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-1885.894</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-4401.598000000002</v>
       </c>
     </row>
     <row r="4">
@@ -2435,36 +2075,48 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-12-31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1614.296</v>
+        <v>-5074.927</v>
       </c>
       <c r="E4" t="n">
-        <v>9731.575999999999</v>
+        <v>22158.7</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-653.4160000000001</v>
+        <v>-9049.683000000001</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-572.405</v>
+        <v>-8790.445</v>
       </c>
       <c r="M4" t="n">
-        <v>-392.392</v>
+        <v>1698.923</v>
       </c>
       <c r="N4" t="n">
+        <v>12032.635</v>
+      </c>
+      <c r="O4" t="n">
+        <v>942.5680000000004</v>
+      </c>
+      <c r="P4" t="n">
         <v>31828.332</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12032.635</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-11090.067</v>
       </c>
     </row>
     <row r="5">
@@ -2473,36 +2125,48 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-12-31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-691.282</v>
+        <v>-15106.533</v>
       </c>
       <c r="E5" t="n">
-        <v>7008.447</v>
+        <v>27854.801</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-6553.666</v>
+        <v>-21429.065</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>8.602</v>
+        <v>20282.878</v>
       </c>
       <c r="M5" t="n">
-        <v>-17.107</v>
+        <v>179.863</v>
       </c>
       <c r="N5" t="n">
+        <v>7356.046</v>
+      </c>
+      <c r="O5" t="n">
+        <v>11781.944</v>
+      </c>
+      <c r="P5" t="n">
         <v>39184.378</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7356.045999999998</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4425.898000000003</v>
       </c>
     </row>
     <row r="6">
@@ -2511,36 +2175,48 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-12-31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>221.121</v>
+        <v>-15563.288</v>
       </c>
       <c r="E6" t="n">
-        <v>13671.946</v>
+        <v>34925.161</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-2758.67</v>
+        <v>-14877.571</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>8.346</v>
+        <v>2114.291</v>
       </c>
       <c r="M6" t="n">
-        <v>-34.728</v>
+        <v>32.201</v>
       </c>
       <c r="N6" t="n">
+        <v>9245.779</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6630.794</v>
+      </c>
+      <c r="P6" t="n">
         <v>48430.157</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>9245.779000000002</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-2614.985000000002</v>
       </c>
     </row>
     <row r="7">
@@ -2549,38 +2225,50 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2000-12-01</t>
+          <t>2000-12-31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-90.184</v>
+        <v>-26539.148</v>
       </c>
       <c r="E7" t="n">
-        <v>9094.619000000001</v>
+        <v>21398.839</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-1941.905</v>
+        <v>4402.641</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-614.971</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-127.452</v>
+        <v>1478.559</v>
       </c>
       <c r="M7" t="n">
-        <v>20.253</v>
+        <v>-839.2619999999999</v>
       </c>
       <c r="N7" t="n">
+        <v>-743.944</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-713.3420000000015</v>
+      </c>
+      <c r="P7" t="n">
         <v>47686.213</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-743.9439999999959</v>
+      </c>
+      <c r="R7" t="n">
+        <v>30.6019999999944</v>
       </c>
     </row>
     <row r="8">
@@ -2589,24 +2277,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8397.878000000001</v>
+        <v>-11944.926</v>
       </c>
       <c r="E8" t="n">
-        <v>1536.537</v>
+        <v>41318.272</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>-2232.312</v>
+        <v>-18572.367</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
@@ -2614,13 +2302,25 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>-614.102</v>
+        <v>-1806.911</v>
       </c>
       <c r="M8" t="n">
-        <v>-66.297</v>
+        <v>-3424.281</v>
       </c>
       <c r="N8" t="n">
+        <v>5569.758</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5569.786999999999</v>
+      </c>
+      <c r="P8" t="n">
         <v>53255.971</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5569.757999999994</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0290000000049985</v>
       </c>
     </row>
     <row r="9">
@@ -2629,40 +2329,52 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-12-31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>196.734</v>
+        <v>-20483.697</v>
       </c>
       <c r="E9" t="n">
-        <v>15954.153</v>
+        <v>90722.091</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-4981.6</v>
+        <v>-26426.605</v>
       </c>
       <c r="I9" t="n">
-        <v>1707.304</v>
+        <v>10564.64</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9320000000000001</v>
+        <v>400.375</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>-276.31</v>
+        <v>-33769.655</v>
       </c>
       <c r="M9" t="n">
-        <v>143.984</v>
+        <v>-1338.211</v>
       </c>
       <c r="N9" t="n">
+        <v>20046.301</v>
+      </c>
+      <c r="O9" t="n">
+        <v>19668.93800000001</v>
+      </c>
+      <c r="P9" t="n">
         <v>73302.272</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>20046.301</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-377.3629999999939</v>
       </c>
     </row>
     <row r="10">
@@ -2671,40 +2383,52 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-12-31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11711.648</v>
+        <v>-1064.493</v>
       </c>
       <c r="E10" t="n">
-        <v>3231.403</v>
+        <v>11180.802</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>13.499</v>
+        <v>643.224</v>
       </c>
       <c r="I10" t="n">
-        <v>-2507.953</v>
+        <v>-15632.065</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.965</v>
+        <v>2.247</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>-1665.84</v>
+        <v>6729.147</v>
       </c>
       <c r="M10" t="n">
-        <v>22.977</v>
+        <v>-1941.998</v>
       </c>
       <c r="N10" t="n">
+        <v>-83.136</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-83.13600000000088</v>
+      </c>
+      <c r="P10" t="n">
         <v>73219.136</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-83.1359999999986</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-2.273736754432321e-12</v>
       </c>
     </row>
     <row r="11">
@@ -2713,40 +2437,52 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-2788.872</v>
+        <v>-48292.47</v>
       </c>
       <c r="E11" t="n">
-        <v>12183.568</v>
+        <v>57838.483</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>7186.047</v>
+        <v>14556.008</v>
       </c>
       <c r="I11" t="n">
-        <v>-1581.56</v>
+        <v>-6032.014</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.331</v>
+        <v>-7.14</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>-1577.674</v>
+        <v>-2400.391</v>
       </c>
       <c r="M11" t="n">
-        <v>214.898</v>
+        <v>-148.935</v>
       </c>
       <c r="N11" t="n">
+        <v>15513.541</v>
+      </c>
+      <c r="O11" t="n">
+        <v>15513.541</v>
+      </c>
+      <c r="P11" t="n">
         <v>88732.677</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>15513.541</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5.456968210637569e-12</v>
       </c>
     </row>
     <row r="12">
@@ -2755,40 +2491,52 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1519.602</v>
+        <v>-43007.731</v>
       </c>
       <c r="E12" t="n">
-        <v>9945.445</v>
+        <v>2808.482</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>9261.061</v>
+        <v>52394.883</v>
       </c>
       <c r="I12" t="n">
-        <v>-172.064</v>
+        <v>-2684.423</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.102</v>
+        <v>-3.343</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>-1927.55</v>
+        <v>2373.784</v>
       </c>
       <c r="M12" t="n">
-        <v>144.777</v>
+        <v>632.9059999999999</v>
       </c>
       <c r="N12" t="n">
+        <v>12514.558</v>
+      </c>
+      <c r="O12" t="n">
+        <v>12514.558</v>
+      </c>
+      <c r="P12" t="n">
         <v>101247.235</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>12514.558</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2797,40 +2545,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-2159.061</v>
+        <v>-59510.709</v>
       </c>
       <c r="E13" t="n">
-        <v>13309.467</v>
+        <v>-686.574</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>5568.509</v>
+        <v>74368.942</v>
       </c>
       <c r="I13" t="n">
-        <v>498.916</v>
+        <v>5436.454</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.039</v>
+        <v>-1.476</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-1645.963</v>
+        <v>-764.37</v>
       </c>
       <c r="M13" t="n">
-        <v>195.164</v>
+        <v>1012.499</v>
       </c>
       <c r="N13" t="n">
+        <v>19854.766</v>
+      </c>
+      <c r="O13" t="n">
+        <v>19854.76599999999</v>
+      </c>
+      <c r="P13" t="n">
         <v>121102.001</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>19854.766</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-1.091393642127514e-11</v>
       </c>
     </row>
     <row r="14">
@@ -2839,40 +2599,52 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-12-31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-4826.282</v>
+        <v>-55600.882</v>
       </c>
       <c r="E14" t="n">
-        <v>19229.181</v>
+        <v>-73974.527</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>4210.354</v>
+        <v>155390.627</v>
       </c>
       <c r="I14" t="n">
-        <v>484.911</v>
+        <v>8812.156000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.05</v>
+        <v>-3.017</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>-3466.24</v>
+        <v>-10600.939</v>
       </c>
       <c r="M14" t="n">
-        <v>137.516</v>
+        <v>1491.448</v>
       </c>
       <c r="N14" t="n">
+        <v>25514.866</v>
+      </c>
+      <c r="O14" t="n">
+        <v>25514.86600000001</v>
+      </c>
+      <c r="P14" t="n">
         <v>146616.867</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>25514.86599999999</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.818989403545856e-11</v>
       </c>
     </row>
     <row r="15">
@@ -2881,40 +2653,52 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-12-31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-3477.074</v>
+        <v>-74312.39599999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-18947.937</v>
+        <v>34058.554</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-7846.766</v>
+        <v>-12124.211</v>
       </c>
       <c r="I15" t="n">
-        <v>983.582</v>
+        <v>-4801.25</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.007</v>
+        <v>-1.073</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>44336.711</v>
+        <v>57041.22</v>
       </c>
       <c r="M15" t="n">
-        <v>182.436</v>
+        <v>1071.994</v>
       </c>
       <c r="N15" t="n">
+        <v>932.838</v>
+      </c>
+      <c r="O15" t="n">
+        <v>932.8380000000044</v>
+      </c>
+      <c r="P15" t="n">
         <v>147549.705</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>932.8379999999888</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.568878360558301e-11</v>
       </c>
     </row>
     <row r="16">
@@ -2923,40 +2707,52 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-12-31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-15185.319</v>
+        <v>-52311.507</v>
       </c>
       <c r="E16" t="n">
-        <v>19521.306</v>
+        <v>11280.602</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>6337.003</v>
+        <v>62936.723</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-3198.916</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.031</v>
+        <v>-1.181</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>-2009.398</v>
+        <v>-3425.469</v>
       </c>
       <c r="M16" t="n">
-        <v>541.211</v>
+        <v>3242.878</v>
       </c>
       <c r="N16" t="n">
+        <v>18523.13</v>
+      </c>
+      <c r="O16" t="n">
+        <v>18523.13</v>
+      </c>
+      <c r="P16" t="n">
         <v>166072.835</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>18523.13</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-7.275957614183426e-12</v>
       </c>
     </row>
     <row r="17">
@@ -2965,40 +2761,52 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2010-12-01</t>
+          <t>2010-12-31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-22880.052</v>
+        <v>-51203.673</v>
       </c>
       <c r="E17" t="n">
-        <v>111543.835</v>
+        <v>249513.458</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>4276.126</v>
+        <v>75552.632</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-134.314</v>
+        <v>-0.539</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>-65142.76</v>
+        <v>-236911.071</v>
       </c>
       <c r="M17" t="n">
-        <v>704.9690000000001</v>
+        <v>3829.68</v>
       </c>
       <c r="N17" t="n">
+        <v>40780.487</v>
+      </c>
+      <c r="O17" t="n">
+        <v>40780.48700000003</v>
+      </c>
+      <c r="P17" t="n">
         <v>206853.322</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>40780.487</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3.637978807091713e-11</v>
       </c>
     </row>
     <row r="18">
@@ -3007,40 +2815,52 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2011-12-01</t>
+          <t>2011-12-31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-17945.76</v>
+        <v>-125632.863</v>
       </c>
       <c r="E18" t="n">
-        <v>44910.037</v>
+        <v>70196.20299999999</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>303.625</v>
+        <v>85156.228</v>
       </c>
       <c r="I18" t="n">
-        <v>-31.85</v>
+        <v>-705.683</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.001</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>4361.607</v>
+        <v>-24388.014</v>
       </c>
       <c r="M18" t="n">
-        <v>-33.262</v>
+        <v>2756.678</v>
       </c>
       <c r="N18" t="n">
+        <v>7381.989</v>
+      </c>
+      <c r="O18" t="n">
+        <v>7381.988999999998</v>
+      </c>
+      <c r="P18" t="n">
         <v>214235.311</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7381.989000000001</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-3.637978807091713e-12</v>
       </c>
     </row>
     <row r="19">
@@ -3049,40 +2869,52 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2012-12-01</t>
+          <t>2012-12-31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-39380.522</v>
+        <v>-121648.972</v>
       </c>
       <c r="E19" t="n">
-        <v>64648.943</v>
+        <v>5653.172</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>-10975.444</v>
+        <v>25896.973</v>
       </c>
       <c r="I19" t="n">
-        <v>-59.77</v>
+        <v>-1100.801</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.424</v>
+        <v>45.943</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>3161.327</v>
+        <v>118682.701</v>
       </c>
       <c r="M19" t="n">
-        <v>6957.731</v>
+        <v>-8392.875</v>
       </c>
       <c r="N19" t="n">
+        <v>19136.141</v>
+      </c>
+      <c r="O19" t="n">
+        <v>19136.141</v>
+      </c>
+      <c r="P19" t="n">
         <v>233371.452</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>19136.141</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3091,40 +2923,52 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2013-12-01</t>
+          <t>2013-12-31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-43098.963</v>
+        <v>-127554.789</v>
       </c>
       <c r="E20" t="n">
-        <v>88570.25199999999</v>
+        <v>197242.065</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-6973.532</v>
+        <v>-22428.624</v>
       </c>
       <c r="I20" t="n">
-        <v>48.593</v>
+        <v>1314.564</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.002</v>
+        <v>-1.675</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>-7111.959</v>
+        <v>-19903.346</v>
       </c>
       <c r="M20" t="n">
-        <v>2528.586</v>
+        <v>-12532.941</v>
       </c>
       <c r="N20" t="n">
+        <v>16138.326</v>
+      </c>
+      <c r="O20" t="n">
+        <v>16135.254</v>
+      </c>
+      <c r="P20" t="n">
         <v>249509.778</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>16138.326</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-3.072000000005573</v>
       </c>
     </row>
     <row r="21">
@@ -3133,40 +2977,52 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2014-12-31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-17938.494</v>
+        <v>-668.486</v>
       </c>
       <c r="E21" t="n">
-        <v>43320.612</v>
+        <v>-76307.204</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>-27192.559</v>
+        <v>16274.839</v>
       </c>
       <c r="I21" t="n">
-        <v>17044.874</v>
+        <v>17329.053</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.045</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>6483.102</v>
+        <v>56163.369</v>
       </c>
       <c r="M21" t="n">
-        <v>185.497</v>
+        <v>1227.406</v>
       </c>
       <c r="N21" t="n">
+        <v>14018.739</v>
+      </c>
+      <c r="O21" t="n">
+        <v>14018.932</v>
+      </c>
+      <c r="P21" t="n">
         <v>263528.517</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>14018.739</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.1929999999956635</v>
       </c>
     </row>
     <row r="22">
@@ -3175,44 +3031,56 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-12-31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>31966.901</v>
+        <v>59665.808</v>
       </c>
       <c r="E22" t="n">
-        <v>-18963.647</v>
+        <v>-124016.063</v>
       </c>
       <c r="F22" t="n">
-        <v>-41100.11</v>
+        <v>-123479.463</v>
       </c>
       <c r="G22" t="n">
-        <v>22136.463</v>
+        <v>-536.6</v>
       </c>
       <c r="H22" t="n">
-        <v>-1077.38</v>
+        <v>-15037.71</v>
       </c>
       <c r="I22" t="n">
-        <v>7794.459</v>
+        <v>89657.15300000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.959</v>
+        <v>-0.593</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>-7713.625</v>
+        <v>-24740.332</v>
       </c>
       <c r="M22" t="n">
-        <v>437.373</v>
+        <v>6233.098</v>
       </c>
       <c r="N22" t="n">
+        <v>-8239.594999999999</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-8238.63899999999</v>
+      </c>
+      <c r="P22" t="n">
         <v>255288.922</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-8239.595000000001</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.9560000000110448</v>
       </c>
     </row>
     <row r="23">
@@ -3221,44 +3089,56 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-12-31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-52397.634</v>
+        <v>12284.191</v>
       </c>
       <c r="E23" t="n">
-        <v>79414.034</v>
+        <v>32267.88</v>
       </c>
       <c r="F23" t="n">
-        <v>7559.278</v>
+        <v>31896.944</v>
       </c>
       <c r="G23" t="n">
-        <v>71854.75599999999</v>
+        <v>370.936</v>
       </c>
       <c r="H23" t="n">
-        <v>352.478</v>
+        <v>32532.733</v>
       </c>
       <c r="I23" t="n">
-        <v>-3858.12</v>
+        <v>-75562.37300000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.027</v>
+        <v>-3.179</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>1612.164</v>
+        <v>6054.528</v>
       </c>
       <c r="M23" t="n">
-        <v>244.327</v>
+        <v>7424.617</v>
       </c>
       <c r="N23" t="n">
+        <v>14998.224</v>
+      </c>
+      <c r="O23" t="n">
+        <v>14998.397</v>
+      </c>
+      <c r="P23" t="n">
         <v>270287.146</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>14998.22400000002</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.172999999980675</v>
       </c>
     </row>
     <row r="24">
@@ -3267,44 +3147,56 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7163.59</v>
+        <v>52132.877</v>
       </c>
       <c r="E24" t="n">
-        <v>45249.193</v>
+        <v>-26792.966</v>
       </c>
       <c r="F24" t="n">
-        <v>-30684.804</v>
+        <v>-111168.532</v>
       </c>
       <c r="G24" t="n">
-        <v>75933.997</v>
+        <v>84375.56600000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-26027.013</v>
+        <v>1396.743</v>
       </c>
       <c r="I24" t="n">
-        <v>1443.181</v>
+        <v>-7032.535</v>
       </c>
       <c r="J24" t="n">
-        <v>-8.92</v>
+        <v>-0.181</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>4770.938</v>
+        <v>867.627</v>
       </c>
       <c r="M24" t="n">
-        <v>-55.314</v>
+        <v>5896.818</v>
       </c>
       <c r="N24" t="n">
+        <v>26468.31</v>
+      </c>
+      <c r="O24" t="n">
+        <v>26468.383</v>
+      </c>
+      <c r="P24" t="n">
         <v>296755.456</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>26468.31</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.0730000000003201</v>
       </c>
     </row>
     <row r="25">
@@ -3313,44 +3205,56 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-12-31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>20453.395</v>
+        <v>-44486.13</v>
       </c>
       <c r="E25" t="n">
-        <v>36530.769</v>
+        <v>35093.592</v>
       </c>
       <c r="F25" t="n">
-        <v>-29615.079</v>
+        <v>32704.358</v>
       </c>
       <c r="G25" t="n">
-        <v>66145.848</v>
+        <v>2389.234</v>
       </c>
       <c r="H25" t="n">
-        <v>-30488.34</v>
+        <v>-17348.77</v>
       </c>
       <c r="I25" t="n">
-        <v>1519.905</v>
+        <v>15125.016</v>
       </c>
       <c r="J25" t="n">
-        <v>13.279</v>
+        <v>13.2</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>-6759.022</v>
+        <v>13987.567</v>
       </c>
       <c r="M25" t="n">
-        <v>1520.697</v>
+        <v>2909.758</v>
       </c>
       <c r="N25" t="n">
+        <v>5294.005</v>
+      </c>
+      <c r="O25" t="n">
+        <v>5294.232999999998</v>
+      </c>
+      <c r="P25" t="n">
         <v>302049.461</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5294.005000000005</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.227999999993699</v>
       </c>
     </row>
     <row r="26">
@@ -3359,44 +3263,56 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-12-31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-43975.649</v>
+        <v>-89301.052</v>
       </c>
       <c r="E26" t="n">
-        <v>127568.06</v>
+        <v>227324.959</v>
       </c>
       <c r="F26" t="n">
-        <v>-15623.582</v>
+        <v>-15720.656</v>
       </c>
       <c r="G26" t="n">
-        <v>143191.642</v>
+        <v>243045.615</v>
       </c>
       <c r="H26" t="n">
-        <v>-46838.632</v>
+        <v>-141168.328</v>
       </c>
       <c r="I26" t="n">
-        <v>-6928.091</v>
+        <v>7639.551</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.06</v>
+        <v>-14.549</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>-6659.602</v>
+        <v>16690.766</v>
       </c>
       <c r="M26" t="n">
-        <v>-3362.213</v>
+        <v>-6634.019</v>
       </c>
       <c r="N26" t="n">
+        <v>14537.246</v>
+      </c>
+      <c r="O26" t="n">
+        <v>14537.328</v>
+      </c>
+      <c r="P26" t="n">
         <v>316586.707</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>14537.24599999998</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.08200000001306761</v>
       </c>
     </row>
     <row r="27">
@@ -3405,46 +3321,58 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>25213.146</v>
+        <v>704194.5379999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-19509.913</v>
+        <v>-630037.433</v>
       </c>
       <c r="F27" t="n">
-        <v>-179441.373</v>
+        <v>-365463.108</v>
       </c>
       <c r="G27" t="n">
-        <v>159931.46</v>
+        <v>-264574.325</v>
       </c>
       <c r="H27" t="n">
-        <v>-12809.786</v>
+        <v>-117733.553</v>
       </c>
       <c r="I27" t="n">
-        <v>-8028.787</v>
+        <v>40800.821</v>
       </c>
       <c r="J27" t="n">
-        <v>2.383</v>
+        <v>3.485</v>
       </c>
       <c r="K27" t="n">
-        <v>27816.1</v>
+        <v>65828.662</v>
       </c>
       <c r="L27" t="n">
-        <v>3009.625</v>
+        <v>69829.095</v>
       </c>
       <c r="M27" t="n">
-        <v>-1835.66</v>
+        <v>-19343.055</v>
       </c>
       <c r="N27" t="n">
+        <v>114949.946</v>
+      </c>
+      <c r="O27" t="n">
+        <v>113542.56</v>
+      </c>
+      <c r="P27" t="n">
         <v>431536.653</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>114949.946</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-1407.385999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3453,46 +3381,58 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-42883.828</v>
+        <v>-81290.481</v>
       </c>
       <c r="E28" t="n">
-        <v>76002.281</v>
+        <v>182431.271</v>
       </c>
       <c r="F28" t="n">
-        <v>-61753.191</v>
+        <v>-121550.764</v>
       </c>
       <c r="G28" t="n">
-        <v>137755.472</v>
+        <v>303982.035</v>
       </c>
       <c r="H28" t="n">
-        <v>-35033.5</v>
+        <v>-36630.77</v>
       </c>
       <c r="I28" t="n">
-        <v>3983.847</v>
+        <v>22323.949</v>
       </c>
       <c r="J28" t="n">
-        <v>50.194</v>
+        <v>44.99</v>
       </c>
       <c r="K28" t="n">
-        <v>4765.473</v>
+        <v>-52769.578</v>
       </c>
       <c r="L28" t="n">
-        <v>246.624</v>
+        <v>-26059.891</v>
       </c>
       <c r="M28" t="n">
-        <v>-11219.235</v>
+        <v>-30402.627</v>
       </c>
       <c r="N28" t="n">
+        <v>-22353.134</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-22353.13699999998</v>
+      </c>
+      <c r="P28" t="n">
         <v>409183.519</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-22353.13400000002</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-0.0029999999642313</v>
       </c>
     </row>
     <row r="29">
@@ -3501,46 +3441,58 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-35780.006</v>
+        <v>-152518.591</v>
       </c>
       <c r="E29" t="n">
-        <v>139533.68</v>
+        <v>437174.227</v>
       </c>
       <c r="F29" t="n">
-        <v>-22231.419</v>
+        <v>251182.278</v>
       </c>
       <c r="G29" t="n">
-        <v>161765.099</v>
+        <v>185991.949</v>
       </c>
       <c r="H29" t="n">
-        <v>-46541.023</v>
+        <v>-56620.783</v>
       </c>
       <c r="I29" t="n">
-        <v>-5739.568</v>
+        <v>-92265.39999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>26.424</v>
+        <v>-27.398</v>
       </c>
       <c r="K29" t="n">
-        <v>-17642.115</v>
+        <v>9097.299000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>13351.98</v>
+        <v>-54168.5</v>
       </c>
       <c r="M29" t="n">
-        <v>-19082.092</v>
+        <v>-80194.454</v>
       </c>
       <c r="N29" t="n">
+        <v>10476.399</v>
+      </c>
+      <c r="O29" t="n">
+        <v>10476.40000000008</v>
+      </c>
+      <c r="P29" t="n">
         <v>419659.918</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>10476.39900000003</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.0010000000474974</v>
       </c>
     </row>
     <row r="30">
@@ -3549,46 +3501,58 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>80331.787</v>
+        <v>206854.972</v>
       </c>
       <c r="E30" t="n">
-        <v>-18023.368</v>
+        <v>-56588.088</v>
       </c>
       <c r="F30" t="n">
-        <v>-127402.891</v>
+        <v>73732.46000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>109379.523</v>
+        <v>-130320.548</v>
       </c>
       <c r="H30" t="n">
-        <v>233.715</v>
+        <v>78236.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-6628.462</v>
+        <v>-70871.662</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-29.715</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>-33737.198</v>
       </c>
       <c r="L30" t="n">
-        <v>-16363.195</v>
+        <v>-45370.899</v>
       </c>
       <c r="M30" t="n">
-        <v>-22381.99</v>
+        <v>-75435.61500000001</v>
       </c>
       <c r="N30" t="n">
+        <v>3058.71</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3058.705000000031</v>
+      </c>
+      <c r="P30" t="n">
         <v>422718.628</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3058.710000000021</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-0.0049999999901046</v>
       </c>
     </row>
     <row r="31">
@@ -3597,46 +3561,58 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>parcial</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-55712.578</v>
+        <v>65831.935</v>
       </c>
       <c r="E31" t="n">
-        <v>211370.114</v>
+        <v>158704.826</v>
       </c>
       <c r="F31" t="n">
-        <v>-30736.668</v>
+        <v>65135.039</v>
       </c>
       <c r="G31" t="n">
-        <v>242106.782</v>
+        <v>93569.787</v>
       </c>
       <c r="H31" t="n">
-        <v>-186347.058</v>
+        <v>-212477.334</v>
       </c>
       <c r="I31" t="n">
-        <v>19928.148</v>
+        <v>115930.245</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.788</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>-0.021</v>
       </c>
       <c r="L31" t="n">
-        <v>35522.321</v>
+        <v>-706.95</v>
       </c>
       <c r="M31" t="n">
-        <v>-10450.304</v>
+        <v>-98786.795</v>
       </c>
       <c r="N31" t="n">
+        <v>28494.96</v>
+      </c>
+      <c r="O31" t="n">
+        <v>28495.118</v>
+      </c>
+      <c r="P31" t="n">
         <v>451213.588</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>28494.95999999996</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.1580000000394648</v>
       </c>
     </row>
     <row r="32">
@@ -3645,44 +3621,56 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-35402.732</v>
+        <v>94770.505</v>
       </c>
       <c r="E32" t="n">
-        <v>73663.50999999999</v>
+        <v>54036.513</v>
       </c>
       <c r="F32" t="n">
-        <v>-77293.57799999999</v>
+        <v>-376560.608</v>
       </c>
       <c r="G32" t="n">
-        <v>150957.088</v>
+        <v>430597.121</v>
       </c>
       <c r="H32" t="n">
-        <v>-22296.357</v>
+        <v>8357.906000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>18302.009</v>
+        <v>-105895.906</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="L32" t="n">
-        <v>-20160.853</v>
+        <v>45376.981</v>
       </c>
       <c r="M32" t="n">
-        <v>2448.268</v>
+        <v>-100762.164</v>
       </c>
       <c r="N32" t="n">
+        <v>-4116.934</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-4116.188999999999</v>
+      </c>
+      <c r="P32" t="n">
         <v>447096.654</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-4116.934000000008</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.7450000000098953</v>
       </c>
     </row>
     <row r="33">
@@ -3691,7 +3679,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3700,35 +3688,47 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>60858.785</v>
+        <v>131825.207</v>
       </c>
       <c r="E33" t="n">
-        <v>-55189.171</v>
+        <v>-72034.109</v>
       </c>
       <c r="F33" t="n">
-        <v>-125795.713</v>
+        <v>20176.538</v>
       </c>
       <c r="G33" t="n">
-        <v>70606.542</v>
+        <v>-92210.64599999999</v>
       </c>
       <c r="H33" t="n">
-        <v>2919.547</v>
+        <v>52583.317</v>
       </c>
       <c r="I33" t="n">
-        <v>9276.611000000001</v>
+        <v>-62162.632</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
         <v>800</v>
       </c>
       <c r="L33" t="n">
-        <v>3858.149</v>
+        <v>14472.391</v>
       </c>
       <c r="M33" t="n">
-        <v>-19230.225</v>
+        <v>-81478.091</v>
       </c>
       <c r="N33" t="n">
+        <v>-15995.656</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-15993.91699999999</v>
+      </c>
+      <c r="P33" t="n">
         <v>431100.998</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-15995.65599999996</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.738999999972293</v>
       </c>
     </row>
   </sheetData>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1995-12-01</t>
+          <t>1995-12-31</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1995-12-01</t>
+          <t>1995-12-31</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1995-12-01</t>
+          <t>1995-12-31</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1995-12-01</t>
+          <t>1995-12-31</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1995-12-01</t>
+          <t>1995-12-31</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1995-12-01</t>
+          <t>1995-12-31</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1996-12-01</t>
+          <t>1996-12-31</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1996-12-01</t>
+          <t>1996-12-31</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1996-12-01</t>
+          <t>1996-12-31</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1996-12-01</t>
+          <t>1996-12-31</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1996-12-01</t>
+          <t>1996-12-31</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1996-12-01</t>
+          <t>1996-12-31</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-12-31</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-12-31</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-12-31</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-12-31</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-12-31</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-12-31</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-12-31</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-12-31</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-12-31</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-12-31</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-12-31</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-12-31</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-12-31</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-12-31</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-12-31</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-12-31</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-12-31</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-12-31</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2000-12-01</t>
+          <t>2000-12-31</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2000-12-01</t>
+          <t>2000-12-31</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2000-12-01</t>
+          <t>2000-12-31</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2000-12-01</t>
+          <t>2000-12-31</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2000-12-01</t>
+          <t>2000-12-31</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2000-12-01</t>
+          <t>2000-12-31</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2000-12-01</t>
+          <t>2000-12-31</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-12-31</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-12-31</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-12-31</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-12-31</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-12-31</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-12-31</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-12-31</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-12-31</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-12-31</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-12-31</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-12-31</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-12-31</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-12-31</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-12-31</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-12-31</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-12-31</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-12-31</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-12-31</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-12-31</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-12-31</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-12-31</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-12-31</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-12-31</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-12-31</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-12-31</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-12-31</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-12-31</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-12-31</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-12-31</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-12-31</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-12-31</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-12-31</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-12-31</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-12-31</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-12-31</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-12-31</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-12-31</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-12-31</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-12-31</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-12-31</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2010-12-01</t>
+          <t>2010-12-31</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2010-12-01</t>
+          <t>2010-12-31</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2010-12-01</t>
+          <t>2010-12-31</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2010-12-01</t>
+          <t>2010-12-31</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2010-12-01</t>
+          <t>2010-12-31</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2010-12-01</t>
+          <t>2010-12-31</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2010-12-01</t>
+          <t>2010-12-31</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2010-12-01</t>
+          <t>2010-12-31</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2011-12-01</t>
+          <t>2011-12-31</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2011-12-01</t>
+          <t>2011-12-31</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2011-12-01</t>
+          <t>2011-12-31</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2011-12-01</t>
+          <t>2011-12-31</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2011-12-01</t>
+          <t>2011-12-31</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2011-12-01</t>
+          <t>2011-12-31</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2011-12-01</t>
+          <t>2011-12-31</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2011-12-01</t>
+          <t>2011-12-31</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2012-12-01</t>
+          <t>2012-12-31</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2012-12-01</t>
+          <t>2012-12-31</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2012-12-01</t>
+          <t>2012-12-31</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2012-12-01</t>
+          <t>2012-12-31</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2012-12-01</t>
+          <t>2012-12-31</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2012-12-01</t>
+          <t>2012-12-31</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2012-12-01</t>
+          <t>2012-12-31</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2012-12-01</t>
+          <t>2012-12-31</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2013-12-01</t>
+          <t>2013-12-31</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2013-12-01</t>
+          <t>2013-12-31</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2013-12-01</t>
+          <t>2013-12-31</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2013-12-01</t>
+          <t>2013-12-31</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2013-12-01</t>
+          <t>2013-12-31</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2013-12-01</t>
+          <t>2013-12-31</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2013-12-01</t>
+          <t>2013-12-31</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2013-12-01</t>
+          <t>2013-12-31</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2014-12-31</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2014-12-31</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2014-12-31</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2014-12-31</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2014-12-31</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2014-12-31</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2014-12-31</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2014-12-31</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-12-31</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-12-31</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-12-31</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-12-31</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-12-31</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-12-31</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-12-31</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-12-31</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-12-31</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-12-31</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-12-31</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-12-31</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-12-31</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-12-31</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-12-31</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-12-31</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-12-31</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-12-31</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-12-31</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-12-31</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-12-31</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-12-31</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-12-31</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-12-31</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-12-31</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-12-31</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -12610,7 +12610,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-12-31</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-12-31</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-12-31</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-12-31</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-12-31</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-12-31</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-12-31</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-12-31</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-12-31</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-12-31</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-12-31</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-12-31</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-12-31</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-12-31</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13844,7 +13844,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -14036,7 +14036,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -14098,7 +14098,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14180,7 +14180,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -14386,7 +14386,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14900,7 +14900,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -15442,7 +15442,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15476,7 +15476,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -15538,7 +15538,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15668,7 +15668,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>ultimo_07/2024</t>
+          <t>ultimo_31/07/2024</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15956,7 +15956,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -15970,7 +15970,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16100,7 +16100,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -16162,7 +16162,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16244,7 +16244,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -16258,7 +16258,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16292,7 +16292,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -16306,7 +16306,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -16402,7 +16402,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>dezembro</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16436,7 +16436,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>ultimo_06/2026</t>
+          <t>ultimo_30/06/2026</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -16498,7 +16498,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>ultimo_06/2026</t>
+          <t>ultimo_30/06/2026</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>ultimo_06/2026</t>
+          <t>ultimo_30/06/2026</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>ultimo_06/2026</t>
+          <t>ultimo_30/06/2026</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>ultimo_06/2026</t>
+          <t>ultimo_30/06/2026</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16676,7 +16676,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -16690,7 +16690,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>ultimo_06/2026</t>
+          <t>ultimo_30/06/2026</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -16738,7 +16738,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>ultimo_06/2026</t>
+          <t>ultimo_30/06/2026</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -16786,7 +16786,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>ultimo_06/2026</t>
+          <t>ultimo_30/06/2026</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -16820,7 +16820,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>ultimo_06/2026</t>
+          <t>ultimo_30/06/2026</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>ultimo_06/2026</t>
+          <t>ultimo_30/06/2026</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
